--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.70502657230013</v>
+        <v>6.777066817998771</v>
       </c>
       <c r="D2" t="n">
-        <v>41.27400796999681</v>
+        <v>6.707026295124482</v>
       </c>
       <c r="E2" t="n">
-        <v>11.89274696918806</v>
+        <v>1.932571382493059</v>
       </c>
       <c r="F2" t="n">
-        <v>11.90163528890191</v>
+        <v>1.934015734446562</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.6910721316083</v>
+        <v>4.662299221386348</v>
       </c>
       <c r="D3" t="n">
-        <v>28.2956460896772</v>
+        <v>4.598042489572545</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89274696918806</v>
+        <v>1.932571382493059</v>
       </c>
       <c r="F3" t="n">
-        <v>11.90163528890191</v>
+        <v>1.934015734446562</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.413472693816063</v>
+        <v>1.04218931274511</v>
       </c>
       <c r="D4" t="n">
-        <v>6.11040793897689</v>
+        <v>0.9929412900837448</v>
       </c>
       <c r="E4" t="n">
-        <v>11.89274696918806</v>
+        <v>1.932571382493059</v>
       </c>
       <c r="F4" t="n">
-        <v>11.90163528890191</v>
+        <v>1.934015734446562</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.96353416118678</v>
+        <v>4.219074301192852</v>
       </c>
       <c r="D5" t="n">
-        <v>26.36428323655396</v>
+        <v>4.284196025940018</v>
       </c>
       <c r="E5" t="n">
-        <v>11.89274696918806</v>
+        <v>1.932571382493059</v>
       </c>
       <c r="F5" t="n">
-        <v>11.90163528890191</v>
+        <v>1.934015734446562</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.05011608928657</v>
+        <v>5.695643864509067</v>
       </c>
       <c r="D6" t="n">
-        <v>35.18753155441049</v>
+        <v>5.717973877591705</v>
       </c>
       <c r="E6" t="n">
-        <v>11.89274696918806</v>
+        <v>1.932571382493059</v>
       </c>
       <c r="F6" t="n">
-        <v>11.90163528890191</v>
+        <v>1.934015734446562</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
